--- a/output/2026-10-11_17_Serbia_Borski_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-11_17_Serbia_Borski_Impiantistica_aspirazione_industriale.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Player nazionale, nessun legame diretto con Bor; incluso come copertura territoriale nazionale. Verificato via WebFetch.</t>
+          <t>Player nazionale, nessun legame diretto con Bor; incluso come copertura territoriale nazionale. Verificato via WebFetch. [DUPLICATO — vedi anche: 2026-10-06_22_Serbia_Grad_Beograd_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -559,7 +559,6 @@
           <t>Delta Filter d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Arilje (copertura nazionale)</t>
@@ -570,11 +569,9 @@
           <t>Filtrazione industriale - agente Donaldson</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato via WebSearch (ekapija.com, profilo Messe Frankfurt). Telefono/email non reperiti in modo affidabile.</t>
+          <t>Verificato via WebSearch (ekapija.com, profilo Messe Frankfurt). Telefono/email non reperiti in modo affidabile. [DUPLICATO — vedi anche: 2026-10-07_04_Serbia_Mačvanski_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -589,7 +586,6 @@
           <t>JELA STIL (Jela Stil Mašine)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Vrnjačka Banja (copertura nazionale)</t>
@@ -600,8 +596,6 @@
           <t>Produzione dust collector / sistemi aspirazione polveri</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verificato via inserzioni marketplace macchinari (used-machines.com, machineseeker.com). Nessun sito/contatti reperiti.</t>
@@ -634,8 +628,6 @@
           <t>Aspiratori industriali, incl. versioni ATEX</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Filiale ufficiale confermata (impressum sito). Nessun rivenditore specifico a Bor; canale nazionale, non distributore locale radicato.</t>
